--- a/LTL_qty.xlsx
+++ b/LTL_qty.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovannighedini/Desktop/ATLAS/AI_Automation/SAP_cleaning/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/BOL RDC/Data source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B771F8A-394F-C14A-9534-71565359ED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46C15978-587E-4460-BC84-0DB7B83CF2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16160" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="149">
   <si>
     <t>D23_Floor and Wall Tiles</t>
   </si>
@@ -1247,15 +1247,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}">
-  <dimension ref="A1:E144"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E145"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="72" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>28</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1289,15 +1289,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
       <c r="B3" s="12">
-        <v>610010004911</v>
+        <v>610010005235</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -1306,193 +1306,193 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>29</v>
       </c>
       <c r="B4" s="12">
+        <v>610010004911</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="12">
         <v>610010005521</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>19</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="12">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="12">
         <v>610010005234</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="12">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="12">
         <v>610010005471</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="12">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="12">
         <v>610010005522</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7">
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8">
         <v>19</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="12">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="12">
         <v>610010005236</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8">
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="12">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="12">
         <v>610010005470</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>43</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="12">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="12">
         <v>610010005352</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>7</v>
       </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10">
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="12">
         <v>610010005523</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>19</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="12">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="12">
         <v>610010005396</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D12">
-        <v>5</v>
-      </c>
-      <c r="E12">
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="12">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="12">
         <v>610010005472</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="12">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="12">
         <v>610010004712</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>52</v>
-      </c>
-      <c r="D14">
-        <v>5</v>
-      </c>
-      <c r="E14">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="12">
-        <v>600015000035</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1501,77 +1501,77 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="12">
+        <v>600015000035</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="12">
         <v>610010003035</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="12">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="12">
         <v>610010005524</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17">
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="12">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="12">
         <v>610010005474</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C19" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E18">
+      <c r="E19">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="12">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="12">
         <v>610010001760</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="D19">
-        <v>5</v>
-      </c>
-      <c r="E19">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="12">
-        <v>610010001761</v>
-      </c>
-      <c r="C20" t="s">
-        <v>53</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -1580,32 +1580,32 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="12">
+        <v>610010001761</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="12">
         <v>610010005506</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>54</v>
-      </c>
-      <c r="D21">
-        <v>5</v>
-      </c>
-      <c r="E21">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="12">
-        <v>610010002204</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -1614,15 +1614,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="12">
-        <v>610010004704</v>
+        <v>610010002204</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -1631,15 +1631,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24" s="12">
-        <v>610010005508</v>
+        <v>610010004704</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -1648,15 +1648,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="12">
-        <v>610010002822</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
+        <v>610010005508</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -1665,15 +1665,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="12">
-        <v>610010004912</v>
+        <v>610010002822</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -1682,32 +1682,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="12">
+        <v>610010004912</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="12">
         <v>610010002950</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>14</v>
-      </c>
-      <c r="D27">
-        <v>5</v>
-      </c>
-      <c r="E27">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="12">
-        <v>610010002200</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>15</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -1716,15 +1716,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="12">
-        <v>610010002920</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
+        <v>610010002200</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -1733,15 +1733,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="12">
-        <v>610010006074</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>17</v>
+        <v>610010002920</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -1750,636 +1750,636 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="12">
+        <v>610010006074</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="12">
         <v>610010005310</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>57</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>19</v>
       </c>
-      <c r="E31">
+      <c r="E32">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="12">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12">
         <v>610010005271</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>58</v>
       </c>
-      <c r="D32">
-        <v>5</v>
-      </c>
-      <c r="E32">
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="12">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="12">
         <v>610010005295</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>117</v>
       </c>
-      <c r="E33">
+      <c r="E34">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="12">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="12">
         <v>610010005305</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>59</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <v>19</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="12">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="12">
         <v>610010005266</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>60</v>
       </c>
-      <c r="D35">
-        <v>5</v>
-      </c>
-      <c r="E35">
+      <c r="D36">
+        <v>5</v>
+      </c>
+      <c r="E36">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="12">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="12">
         <v>610010005290</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>118</v>
       </c>
-      <c r="E36">
+      <c r="E37">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" s="12">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="12">
         <v>610010005309</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>61</v>
       </c>
-      <c r="D37">
+      <c r="D38">
         <v>19</v>
       </c>
-      <c r="E37">
+      <c r="E38">
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38" s="12">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="12">
         <v>610010005270</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>62</v>
       </c>
-      <c r="D38">
-        <v>5</v>
-      </c>
-      <c r="E38">
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39" s="12">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="12">
         <v>610010005294</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>119</v>
       </c>
-      <c r="E39">
+      <c r="E40">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>29</v>
-      </c>
-      <c r="B40" s="12">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="12">
         <v>610010005307</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D40">
+      <c r="D41">
         <v>19</v>
       </c>
-      <c r="E40">
+      <c r="E41">
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" s="12">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="12">
         <v>610010005268</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>63</v>
       </c>
-      <c r="D41">
-        <v>5</v>
-      </c>
-      <c r="E41">
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" s="12">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="12">
         <v>610010005292</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C43" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E42">
+      <c r="E43">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" s="12">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="12">
         <v>610010001042</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>64</v>
       </c>
-      <c r="D43">
-        <v>5</v>
-      </c>
-      <c r="E43">
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="12">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="12">
         <v>610010004574</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>121</v>
       </c>
-      <c r="E44">
+      <c r="E45">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B45" s="12">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" s="12">
         <v>610010005520</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>18</v>
       </c>
-      <c r="D45">
+      <c r="D46">
         <v>19</v>
       </c>
-      <c r="E45">
+      <c r="E46">
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" s="12">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" s="12">
         <v>610010005394</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C47" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D46">
-        <v>5</v>
-      </c>
-      <c r="E46">
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>29</v>
-      </c>
-      <c r="B47" s="12">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" s="12">
         <v>610010005473</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>122</v>
       </c>
-      <c r="E47">
+      <c r="E48">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>29</v>
-      </c>
-      <c r="B48" s="12">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" s="12">
         <v>610010001040</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>65</v>
       </c>
-      <c r="D48">
-        <v>5</v>
-      </c>
-      <c r="E48">
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>29</v>
-      </c>
-      <c r="B49" s="12">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" s="12">
         <v>610010004572</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>123</v>
       </c>
-      <c r="E49">
+      <c r="E50">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>29</v>
-      </c>
-      <c r="B50" s="12">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51" s="12">
         <v>610010001043</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
         <v>66</v>
       </c>
-      <c r="D50">
-        <v>5</v>
-      </c>
-      <c r="E50">
+      <c r="D51">
+        <v>5</v>
+      </c>
+      <c r="E51">
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" s="12">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" s="12">
         <v>610010004575</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>124</v>
       </c>
-      <c r="E51">
+      <c r="E52">
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B52" s="12">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" s="12">
         <v>610010001039</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>67</v>
       </c>
-      <c r="D52">
-        <v>5</v>
-      </c>
-      <c r="E52">
+      <c r="D53">
+        <v>5</v>
+      </c>
+      <c r="E53">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" s="12">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="12">
         <v>610010004571</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C54" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E53">
+      <c r="E54">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>29</v>
-      </c>
-      <c r="B54" s="12">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B55" s="12">
         <v>610010005313</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>68</v>
       </c>
-      <c r="D54">
+      <c r="D55">
         <v>19</v>
       </c>
-      <c r="E54">
+      <c r="E55">
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>29</v>
-      </c>
-      <c r="B55" s="12">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" s="12">
         <v>610010005274</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C56" t="s">
         <v>69</v>
       </c>
-      <c r="D55">
-        <v>5</v>
-      </c>
-      <c r="E55">
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56">
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>29</v>
-      </c>
-      <c r="B56" s="12">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="12">
         <v>610010005283</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C57" t="s">
         <v>126</v>
       </c>
-      <c r="E56">
+      <c r="E57">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" s="12">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" s="12">
         <v>610010005319</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C58" t="s">
         <v>70</v>
       </c>
-      <c r="D57">
+      <c r="D58">
         <v>19</v>
       </c>
-      <c r="E57">
+      <c r="E58">
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>29</v>
-      </c>
-      <c r="B58" s="12">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="12">
         <v>610010005280</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>71</v>
       </c>
-      <c r="D58">
-        <v>5</v>
-      </c>
-      <c r="E58">
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="E59">
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>29</v>
-      </c>
-      <c r="B59" s="12">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" s="12">
         <v>610010005289</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C60" t="s">
         <v>127</v>
       </c>
-      <c r="E59">
+      <c r="E60">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>29</v>
-      </c>
-      <c r="B60" s="12">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" s="12">
         <v>610010005317</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>72</v>
       </c>
-      <c r="D60">
+      <c r="D61">
         <v>19</v>
       </c>
-      <c r="E60">
+      <c r="E61">
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>29</v>
-      </c>
-      <c r="B61" s="12">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" s="12">
         <v>610010005278</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>73</v>
       </c>
-      <c r="D61">
-        <v>5</v>
-      </c>
-      <c r="E61">
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="E62">
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>29</v>
-      </c>
-      <c r="B62" s="12">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" s="12">
         <v>610010005287</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" t="s">
         <v>128</v>
       </c>
-      <c r="E62">
+      <c r="E63">
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>29</v>
-      </c>
-      <c r="B63" s="12">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>29</v>
+      </c>
+      <c r="B64" s="12">
         <v>610010005318</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>74</v>
       </c>
-      <c r="D63">
+      <c r="D64">
         <v>19</v>
       </c>
-      <c r="E63">
+      <c r="E64">
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>29</v>
-      </c>
-      <c r="B64" s="12">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>29</v>
+      </c>
+      <c r="B65" s="12">
         <v>610010005279</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
         <v>75</v>
       </c>
-      <c r="D64">
-        <v>5</v>
-      </c>
-      <c r="E64">
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>29</v>
-      </c>
-      <c r="B65" s="12">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" s="12">
         <v>610010005288</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>129</v>
       </c>
-      <c r="E65">
+      <c r="E66">
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>29</v>
-      </c>
-      <c r="B66" s="12">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>29</v>
+      </c>
+      <c r="B67" s="12">
         <v>610010005314</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>76</v>
       </c>
-      <c r="D66">
+      <c r="D67">
         <v>19</v>
       </c>
-      <c r="E66">
+      <c r="E67">
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B67" s="12">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>29</v>
+      </c>
+      <c r="B68" s="12">
         <v>610010005275</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>77</v>
       </c>
-      <c r="D67">
-        <v>5</v>
-      </c>
-      <c r="E67">
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68">
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>29</v>
-      </c>
-      <c r="B68" s="12">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" s="12">
         <v>610010005284</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C69" t="s">
         <v>130</v>
       </c>
-      <c r="E68">
+      <c r="E69">
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>29</v>
-      </c>
-      <c r="B69" s="12">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>29</v>
+      </c>
+      <c r="B70" s="12">
         <v>610130007000</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C70" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="D69">
-        <v>16</v>
-      </c>
-      <c r="E69">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" s="12">
-        <v>610130000920</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>23</v>
       </c>
       <c r="D70">
         <v>16</v>
@@ -2388,15 +2388,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>29</v>
       </c>
       <c r="B71" s="12">
-        <v>610130007215</v>
+        <v>610130000920</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D71">
         <v>16</v>
@@ -2405,15 +2405,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>29</v>
       </c>
       <c r="B72" s="12">
-        <v>610130007001</v>
+        <v>610130007215</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D72">
         <v>16</v>
@@ -2422,15 +2422,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>29</v>
       </c>
       <c r="B73" s="12">
-        <v>610130000919</v>
+        <v>610130007001</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D73">
         <v>16</v>
@@ -2439,32 +2439,32 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>29</v>
       </c>
       <c r="B74" s="12">
+        <v>610130000919</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74">
+        <v>16</v>
+      </c>
+      <c r="E74">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>29</v>
+      </c>
+      <c r="B75" s="12">
         <v>610010002391</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C75" t="s">
         <v>78</v>
-      </c>
-      <c r="D74">
-        <v>6</v>
-      </c>
-      <c r="E74">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>29</v>
-      </c>
-      <c r="B75" s="12">
-        <v>610010002393</v>
-      </c>
-      <c r="C75" t="s">
-        <v>79</v>
       </c>
       <c r="D75">
         <v>6</v>
@@ -2473,15 +2473,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>29</v>
       </c>
       <c r="B76" s="12">
-        <v>610010002392</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>80</v>
+        <v>610010002393</v>
+      </c>
+      <c r="C76" t="s">
+        <v>79</v>
       </c>
       <c r="D76">
         <v>6</v>
@@ -2490,32 +2490,32 @@
         <v>56</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>29</v>
       </c>
       <c r="B77" s="12">
-        <v>610010004527</v>
-      </c>
-      <c r="C77" t="s">
-        <v>81</v>
+        <v>610010002392</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="D77">
         <v>6</v>
       </c>
       <c r="E77">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>29</v>
       </c>
       <c r="B78" s="12">
-        <v>610010004530</v>
+        <v>610010004527</v>
       </c>
       <c r="C78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D78">
         <v>6</v>
@@ -2524,15 +2524,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>29</v>
       </c>
       <c r="B79" s="12">
-        <v>610010004905</v>
+        <v>610010004530</v>
       </c>
       <c r="C79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D79">
         <v>6</v>
@@ -2541,15 +2541,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>29</v>
       </c>
       <c r="B80" s="12">
-        <v>610010002361</v>
+        <v>610010004905</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D80">
         <v>6</v>
@@ -2558,15 +2558,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>29</v>
       </c>
       <c r="B81" s="12">
-        <v>610010004901</v>
+        <v>610010002361</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D81">
         <v>6</v>
@@ -2575,15 +2575,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>29</v>
       </c>
       <c r="B82" s="12">
-        <v>610010004900</v>
+        <v>610010004901</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D82">
         <v>6</v>
@@ -2592,15 +2592,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>29</v>
       </c>
       <c r="B83" s="12">
-        <v>610010004902</v>
+        <v>610010004900</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D83">
         <v>6</v>
@@ -2609,15 +2609,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>29</v>
       </c>
       <c r="B84" s="12">
-        <v>610010004906</v>
+        <v>610010004902</v>
       </c>
       <c r="C84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D84">
         <v>6</v>
@@ -2626,15 +2626,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>29</v>
       </c>
       <c r="B85" s="12">
-        <v>610010002360</v>
+        <v>610010004906</v>
       </c>
       <c r="C85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D85">
         <v>6</v>
@@ -2643,49 +2643,49 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>29</v>
       </c>
       <c r="B86" s="12">
-        <v>610010002851</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>50</v>
+        <v>610010002360</v>
+      </c>
+      <c r="C86" t="s">
+        <v>89</v>
       </c>
       <c r="D86">
         <v>6</v>
       </c>
       <c r="E86">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>29</v>
       </c>
       <c r="B87" s="12">
-        <v>610010004582</v>
-      </c>
-      <c r="C87" t="s">
-        <v>90</v>
+        <v>610010002851</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D87">
         <v>6</v>
       </c>
       <c r="E87">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>29</v>
       </c>
       <c r="B88" s="12">
-        <v>610010004581</v>
+        <v>610010004582</v>
       </c>
       <c r="C88" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88">
         <v>6</v>
@@ -2694,15 +2694,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>29</v>
       </c>
       <c r="B89" s="12">
-        <v>610010004580</v>
+        <v>610010004581</v>
       </c>
       <c r="C89" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D89">
         <v>6</v>
@@ -2711,15 +2711,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>29</v>
       </c>
       <c r="B90" s="12">
-        <v>610010004532</v>
+        <v>610010004580</v>
       </c>
       <c r="C90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D90">
         <v>6</v>
@@ -2728,15 +2728,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>29</v>
       </c>
       <c r="B91" s="12">
-        <v>610010002362</v>
+        <v>610010004532</v>
       </c>
       <c r="C91" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D91">
         <v>6</v>
@@ -2745,15 +2745,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>29</v>
       </c>
       <c r="B92" s="12">
-        <v>610010004903</v>
+        <v>610010002362</v>
       </c>
       <c r="C92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D92">
         <v>6</v>
@@ -2762,15 +2762,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>29</v>
       </c>
       <c r="B93" s="12">
-        <v>610010002814</v>
+        <v>610010004903</v>
       </c>
       <c r="C93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D93">
         <v>6</v>
@@ -2779,15 +2779,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>29</v>
       </c>
       <c r="B94" s="12">
-        <v>610010002816</v>
+        <v>610010002814</v>
       </c>
       <c r="C94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D94">
         <v>6</v>
@@ -2796,15 +2796,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>29</v>
       </c>
       <c r="B95" s="12">
-        <v>610010002815</v>
+        <v>610010002816</v>
       </c>
       <c r="C95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D95">
         <v>6</v>
@@ -2813,15 +2813,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>29</v>
       </c>
       <c r="B96" s="12">
-        <v>610010002817</v>
+        <v>610010002815</v>
       </c>
       <c r="C96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D96">
         <v>6</v>
@@ -2830,148 +2830,148 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>29</v>
       </c>
       <c r="B97" s="12">
+        <v>610010002817</v>
+      </c>
+      <c r="C97" t="s">
+        <v>99</v>
+      </c>
+      <c r="D97">
+        <v>6</v>
+      </c>
+      <c r="E97">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>29</v>
+      </c>
+      <c r="B98" s="12">
         <v>610110001402</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C98" t="s">
         <v>27</v>
       </c>
-      <c r="D97">
+      <c r="D98">
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>30</v>
-      </c>
-      <c r="B98" s="12">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>30</v>
+      </c>
+      <c r="B99" s="12">
         <v>600010000961</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C99" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D98">
+      <c r="D99">
         <v>7</v>
       </c>
-      <c r="E98">
+      <c r="E99">
         <v>60</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>30</v>
-      </c>
-      <c r="B99" s="12">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>30</v>
+      </c>
+      <c r="B100" s="12">
         <v>610010004651</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C100" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D99">
+      <c r="D100">
         <v>4</v>
       </c>
-      <c r="E99">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>30</v>
-      </c>
-      <c r="B100" s="12">
+      <c r="E100">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" s="12">
         <v>600010000962</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D100">
+      <c r="D101">
         <v>7</v>
       </c>
-      <c r="E100">
+      <c r="E101">
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>30</v>
-      </c>
-      <c r="B101" s="12">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" s="12">
         <v>610010003151</v>
       </c>
-      <c r="C101" s="5" t="s">
+      <c r="C102" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D101">
-        <v>5</v>
-      </c>
-      <c r="E101">
+      <c r="D102">
+        <v>5</v>
+      </c>
+      <c r="E102">
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>30</v>
-      </c>
-      <c r="B102" s="12">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" s="12">
         <v>610010005863</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C103" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D102">
+      <c r="D103">
         <v>4</v>
       </c>
-      <c r="E102">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>30</v>
-      </c>
-      <c r="B103" s="12">
+      <c r="E103">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104" s="12">
         <v>610010002001</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D103">
+      <c r="D104">
         <v>7</v>
       </c>
-      <c r="E103">
+      <c r="E104">
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>30</v>
-      </c>
-      <c r="B104" s="12">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" s="12">
         <v>610010004650</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="D104">
-        <v>4</v>
-      </c>
-      <c r="E104">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>30</v>
-      </c>
-      <c r="B105" s="12">
-        <v>610010005864</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="D105">
         <v>4</v>
@@ -2980,32 +2980,32 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>30</v>
       </c>
       <c r="B106" s="12">
+        <v>610010005864</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D106">
+        <v>4</v>
+      </c>
+      <c r="E106">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>30</v>
+      </c>
+      <c r="B107" s="12">
         <v>610010002206</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C107" s="13" t="s">
         <v>35</v>
-      </c>
-      <c r="D106">
-        <v>7</v>
-      </c>
-      <c r="E106">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>30</v>
-      </c>
-      <c r="B107" s="12">
-        <v>610010002317</v>
-      </c>
-      <c r="C107" s="13" t="s">
-        <v>36</v>
       </c>
       <c r="D107">
         <v>7</v>
@@ -3014,83 +3014,83 @@
         <v>60</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>30</v>
       </c>
       <c r="B108" s="12">
+        <v>610010002317</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D108">
+        <v>7</v>
+      </c>
+      <c r="E108">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>30</v>
+      </c>
+      <c r="B109" s="12">
         <v>610010004653</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C109" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D108">
+      <c r="D109">
         <v>4</v>
       </c>
-      <c r="E108">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>30</v>
-      </c>
-      <c r="B109" s="12">
+      <c r="E109">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>30</v>
+      </c>
+      <c r="B110" s="12">
         <v>610010005509</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C110" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D109">
+      <c r="D110">
         <v>7</v>
       </c>
-      <c r="E109">
+      <c r="E110">
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>30</v>
-      </c>
-      <c r="B110" s="12">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>30</v>
+      </c>
+      <c r="B111" s="12">
         <v>610010005527</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D110">
+      <c r="D111">
         <v>4</v>
       </c>
-      <c r="E110">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>30</v>
-      </c>
-      <c r="B111" s="12">
+      <c r="E111">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>30</v>
+      </c>
+      <c r="B112" s="12">
         <v>610010002221</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D111">
-        <v>7</v>
-      </c>
-      <c r="E111">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>30</v>
-      </c>
-      <c r="B112" s="12">
-        <v>610010002315</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="D112">
         <v>7</v>
@@ -3099,32 +3099,32 @@
         <v>60</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>30</v>
       </c>
       <c r="B113" s="12">
+        <v>610010002315</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D113">
+        <v>7</v>
+      </c>
+      <c r="E113">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" s="12">
         <v>610010005660</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C114" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="D113">
-        <v>4</v>
-      </c>
-      <c r="E113">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>30</v>
-      </c>
-      <c r="B114" s="12">
-        <v>610010005788</v>
-      </c>
-      <c r="C114" s="14" t="s">
-        <v>107</v>
       </c>
       <c r="D114">
         <v>4</v>
@@ -3133,15 +3133,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>30</v>
       </c>
       <c r="B115" s="12">
-        <v>610010005661</v>
+        <v>610010005788</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D115">
         <v>4</v>
@@ -3150,83 +3150,83 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>30</v>
       </c>
       <c r="B116" s="12">
+        <v>610010005661</v>
+      </c>
+      <c r="C116" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D116">
+        <v>4</v>
+      </c>
+      <c r="E116">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>30</v>
+      </c>
+      <c r="B117" s="12">
         <v>610010002220</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C117" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D116">
+      <c r="D117">
         <v>7</v>
       </c>
-      <c r="E116">
+      <c r="E117">
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>30</v>
-      </c>
-      <c r="B117" s="12">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>30</v>
+      </c>
+      <c r="B118" s="12">
         <v>610010004652</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C118" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D117">
+      <c r="D118">
         <v>4</v>
       </c>
-      <c r="E117">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>30</v>
-      </c>
-      <c r="B118" s="12">
+      <c r="E118">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>30</v>
+      </c>
+      <c r="B119" s="12">
         <v>600010000959</v>
       </c>
-      <c r="C118" s="13" t="s">
+      <c r="C119" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D118">
+      <c r="D119">
         <v>7</v>
       </c>
-      <c r="E118">
+      <c r="E119">
         <v>60</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>30</v>
-      </c>
-      <c r="B119" s="12">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>30</v>
+      </c>
+      <c r="B120" s="12">
         <v>610010005866</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C120" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D119">
-        <v>4</v>
-      </c>
-      <c r="E119">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>30</v>
-      </c>
-      <c r="B120" s="12">
-        <v>610010005865</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -3235,15 +3235,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>30</v>
       </c>
       <c r="B121" s="12">
-        <v>610010005526</v>
+        <v>610010005865</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D121">
         <v>4</v>
@@ -3252,15 +3252,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>30</v>
       </c>
       <c r="B122" s="12">
-        <v>610010005571</v>
+        <v>610010005526</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D122">
         <v>4</v>
@@ -3269,15 +3269,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>30</v>
       </c>
       <c r="B123" s="12">
-        <v>610010005913</v>
+        <v>610010005571</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D123">
         <v>4</v>
@@ -3286,15 +3286,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>30</v>
       </c>
       <c r="B124" s="12">
-        <v>610010005912</v>
+        <v>610010005913</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D124">
         <v>4</v>
@@ -3303,15 +3303,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>30</v>
       </c>
       <c r="B125" s="12">
-        <v>610010005570</v>
+        <v>610010005912</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D125">
         <v>4</v>
@@ -3320,15 +3320,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>30</v>
       </c>
       <c r="B126" s="12">
-        <v>610010005525</v>
+        <v>610010005570</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D126">
         <v>4</v>
@@ -3337,60 +3337,60 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B127" s="12">
+        <v>610010005525</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D127">
+        <v>4</v>
+      </c>
+      <c r="E127">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>29</v>
+      </c>
+      <c r="B128" s="12">
         <v>610010006068</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="E127">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
-        <v>29</v>
-      </c>
-      <c r="B128" s="12">
-        <v>610010006069</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="E128">
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>29</v>
       </c>
       <c r="B129" s="12">
+        <v>610010006069</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E129">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>29</v>
+      </c>
+      <c r="B130" s="12">
         <v>610010006070</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C130" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D129">
-        <v>5</v>
-      </c>
-      <c r="E129">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
-        <v>29</v>
-      </c>
-      <c r="B130" s="12">
-        <v>610010006073</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="D130">
         <v>5</v>
@@ -3399,46 +3399,46 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>29</v>
       </c>
       <c r="B131" s="12">
+        <v>610010006073</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D131">
+        <v>5</v>
+      </c>
+      <c r="E131">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>29</v>
+      </c>
+      <c r="B132" s="12">
         <v>610010005960</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E131">
+      <c r="E132">
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>29</v>
-      </c>
-      <c r="B132" s="12">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>29</v>
+      </c>
+      <c r="B133" s="12">
         <v>610010006071</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="D132">
-        <v>5</v>
-      </c>
-      <c r="E132">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>29</v>
-      </c>
-      <c r="B133" s="12">
-        <v>610010006072</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="D133">
         <v>5</v>
@@ -3447,32 +3447,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>29</v>
       </c>
       <c r="B134" s="12">
+        <v>610010006072</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D134">
+        <v>5</v>
+      </c>
+      <c r="E134">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>29</v>
+      </c>
+      <c r="B135" s="12">
         <v>610010006057</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="D134">
-        <v>5</v>
-      </c>
-      <c r="E134">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>29</v>
-      </c>
-      <c r="B135" s="12">
-        <v>610010006058</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D135">
         <v>5</v>
@@ -3481,63 +3481,63 @@
         <v>36</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>29</v>
       </c>
       <c r="B136" s="12">
+        <v>610010006058</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D136">
+        <v>5</v>
+      </c>
+      <c r="E136">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>29</v>
+      </c>
+      <c r="B137" s="12">
         <v>610010005867</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D136">
-        <v>5</v>
-      </c>
-      <c r="E136">
+      <c r="D137">
+        <v>5</v>
+      </c>
+      <c r="E137">
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>29</v>
-      </c>
-      <c r="B137" s="12">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>29</v>
+      </c>
+      <c r="B138" s="12">
         <v>610010006101</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E137">
+      <c r="E138">
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>29</v>
-      </c>
-      <c r="B138" s="12">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>29</v>
+      </c>
+      <c r="B139" s="12">
         <v>610010005779</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C139" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="D138">
-        <v>5</v>
-      </c>
-      <c r="E138">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>29</v>
-      </c>
-      <c r="B139" s="12">
-        <v>610010005781</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D139">
         <v>5</v>
@@ -3546,46 +3546,46 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>29</v>
       </c>
       <c r="B140" s="12">
+        <v>610010005781</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D140">
+        <v>5</v>
+      </c>
+      <c r="E140">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>29</v>
+      </c>
+      <c r="B141" s="12">
         <v>610010006054</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E140">
+      <c r="E141">
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>29</v>
-      </c>
-      <c r="B141" s="12">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>29</v>
+      </c>
+      <c r="B142" s="12">
         <v>610010006097</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C142" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="D141">
-        <v>5</v>
-      </c>
-      <c r="E141">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>29</v>
-      </c>
-      <c r="B142" s="12">
-        <v>610010006098</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="D142">
         <v>5</v>
@@ -3594,15 +3594,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>29</v>
       </c>
       <c r="B143" s="12">
-        <v>610010005272</v>
+        <v>610010006098</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D143">
         <v>5</v>
@@ -3611,42 +3611,59 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B144" s="12"/>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>29</v>
+      </c>
+      <c r="B144" s="12">
+        <v>610010005272</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D144">
+        <v>5</v>
+      </c>
+      <c r="E144">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B145" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E126" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
-  <conditionalFormatting sqref="B2:B143">
+  <autoFilter ref="A1:E127" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
+  <conditionalFormatting sqref="B2:B144">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" xr:uid="{89506ED6-C4FD-47B8-9FD6-878DCA92E9AA}"/>
-    <hyperlink ref="C18" r:id="rId2" xr:uid="{7B1ECE4D-B039-4F94-838C-A478D53267E0}"/>
-    <hyperlink ref="C86" r:id="rId3" xr:uid="{DBB2C1A8-C8F2-410F-A78B-A3CD9BB920C8}"/>
-    <hyperlink ref="C98" r:id="rId4" xr:uid="{DD3336F3-63B5-4EA8-91C3-0AEEB13315C2}"/>
-    <hyperlink ref="C106" r:id="rId5" xr:uid="{8BD8BB4A-70AA-4FA9-9A46-A3355CDFBD57}"/>
-    <hyperlink ref="C99" r:id="rId6" xr:uid="{4FEA0A94-1AD0-4B82-ABB9-6EDBB77929EF}"/>
-    <hyperlink ref="C107:C109" r:id="rId7" display="Bluestone Natural Cleft 24x24" xr:uid="{9D1D11EE-261B-43AD-B4EF-C3FA544A4E70}"/>
-    <hyperlink ref="C116" r:id="rId8" xr:uid="{D42B3E22-C339-41A5-BEA6-DF49B989F449}"/>
-    <hyperlink ref="C118" r:id="rId9" xr:uid="{2B8374D8-0246-4EE4-B96B-FFB02E40BDD1}"/>
-    <hyperlink ref="C107" r:id="rId10" xr:uid="{14C18384-D389-4B97-8461-5247EE585E74}"/>
-    <hyperlink ref="C108" r:id="rId11" xr:uid="{9272B80D-012D-439F-9BD1-11D9279BF6BE}"/>
-    <hyperlink ref="C109" r:id="rId12" xr:uid="{382FF713-4781-44B6-B266-152BC4F3E727}"/>
-    <hyperlink ref="C127" r:id="rId13" tooltip="https://www.homedepot.com/p/339947207" display="https://www.homedepot.com/p/339947207" xr:uid="{9AD5B75B-E88A-1A44-8BE7-A67673DAF7E8}"/>
-    <hyperlink ref="C128" r:id="rId14" tooltip="https://www.homedepot.com/p/339927439" display="https://www.homedepot.com/p/339927439" xr:uid="{4447D77D-1EA3-2348-AF81-58EFF7EEA8FA}"/>
-    <hyperlink ref="C129" r:id="rId15" tooltip="https://www.homedepot.com/p/339927440" display="https://www.homedepot.com/p/339927440" xr:uid="{34AFCD0E-8C12-A24A-828F-22505A90BE5F}"/>
-    <hyperlink ref="C130" r:id="rId16" tooltip="https://www.homedepot.com/p/339927441" display="https://www.homedepot.com/p/339927441" xr:uid="{91E7067B-523B-0543-BA7A-39DAE4E57F84}"/>
-    <hyperlink ref="C131" r:id="rId17" tooltip="https://www.homedepot.com/p/339927442" display="https://www.homedepot.com/p/339927442" xr:uid="{94ED3BB9-4382-B140-A9AA-8E2AFE42F2CF}"/>
-    <hyperlink ref="C132" r:id="rId18" tooltip="https://www.homedepot.com/p/339947312" display="https://www.homedepot.com/p/339947312" xr:uid="{D096ABEE-929C-8148-96F1-0DB77A7A4CA0}"/>
-    <hyperlink ref="C133" r:id="rId19" tooltip="https://www.homedepot.com/p/339927437" display="https://www.homedepot.com/p/339927437" xr:uid="{A7D2EEFA-BCE1-DA4A-93A0-BCC21EADC083}"/>
-    <hyperlink ref="C136" r:id="rId20" tooltip="http://www.homedepot.com/p/340312493" display="http://www.homedepot.com/p/340312493" xr:uid="{8BFD45A8-6B97-374E-A2E6-FA1EE0780DD6}"/>
-    <hyperlink ref="C137" r:id="rId21" tooltip="http://www.homedepot.com/p/340312481" display="http://www.homedepot.com/p/340312481" xr:uid="{7DA9E60B-FA8B-B549-8795-458ABD8B8A3D}"/>
-    <hyperlink ref="C138" r:id="rId22" tooltip="http://www.homedepot.com/p/340312476" display="http://www.homedepot.com/p/340312476" xr:uid="{F0B765B7-2EC2-9940-8CD8-248995C37761}"/>
-    <hyperlink ref="C139" r:id="rId23" tooltip="http://www.homedepot.com/p/340312489" display="http://www.homedepot.com/p/340312489" xr:uid="{B4E49CEA-5F25-0842-B5F2-A37995C490F1}"/>
-    <hyperlink ref="C140" r:id="rId24" tooltip="http://www.homedepot.com/p/340312486" display="http://www.homedepot.com/p/340312486" xr:uid="{F30F8C7B-779D-5A44-BD65-45F9B426C034}"/>
-    <hyperlink ref="C141" r:id="rId25" tooltip="http://www.homedepot.com/p/340312477" display="http://www.homedepot.com/p/340312477" xr:uid="{506B9C18-7659-C14A-ABCB-524662575D4D}"/>
-    <hyperlink ref="C142" r:id="rId26" tooltip="http://www.homedepot.com/p/340312479" display="http://www.homedepot.com/p/340312479" xr:uid="{75E6409F-9A58-B849-8E19-4E18B096902B}"/>
-    <hyperlink ref="C143" r:id="rId27" tooltip="http://www.homedepot.com/p/340312491" display="http://www.homedepot.com/p/340312491" xr:uid="{33BDB607-F61F-A74A-AFCE-5492A651B2B9}"/>
+    <hyperlink ref="C9" r:id="rId1" xr:uid="{89506ED6-C4FD-47B8-9FD6-878DCA92E9AA}"/>
+    <hyperlink ref="C19" r:id="rId2" xr:uid="{7B1ECE4D-B039-4F94-838C-A478D53267E0}"/>
+    <hyperlink ref="C87" r:id="rId3" xr:uid="{DBB2C1A8-C8F2-410F-A78B-A3CD9BB920C8}"/>
+    <hyperlink ref="C99" r:id="rId4" xr:uid="{DD3336F3-63B5-4EA8-91C3-0AEEB13315C2}"/>
+    <hyperlink ref="C107" r:id="rId5" xr:uid="{8BD8BB4A-70AA-4FA9-9A46-A3355CDFBD57}"/>
+    <hyperlink ref="C100" r:id="rId6" xr:uid="{4FEA0A94-1AD0-4B82-ABB9-6EDBB77929EF}"/>
+    <hyperlink ref="C108:C110" r:id="rId7" display="Bluestone Natural Cleft 24x24" xr:uid="{9D1D11EE-261B-43AD-B4EF-C3FA544A4E70}"/>
+    <hyperlink ref="C117" r:id="rId8" xr:uid="{D42B3E22-C339-41A5-BEA6-DF49B989F449}"/>
+    <hyperlink ref="C119" r:id="rId9" xr:uid="{2B8374D8-0246-4EE4-B96B-FFB02E40BDD1}"/>
+    <hyperlink ref="C108" r:id="rId10" xr:uid="{14C18384-D389-4B97-8461-5247EE585E74}"/>
+    <hyperlink ref="C109" r:id="rId11" xr:uid="{9272B80D-012D-439F-9BD1-11D9279BF6BE}"/>
+    <hyperlink ref="C110" r:id="rId12" xr:uid="{382FF713-4781-44B6-B266-152BC4F3E727}"/>
+    <hyperlink ref="C128" r:id="rId13" tooltip="https://www.homedepot.com/p/339947207" display="https://www.homedepot.com/p/339947207" xr:uid="{9AD5B75B-E88A-1A44-8BE7-A67673DAF7E8}"/>
+    <hyperlink ref="C129" r:id="rId14" tooltip="https://www.homedepot.com/p/339927439" display="https://www.homedepot.com/p/339927439" xr:uid="{4447D77D-1EA3-2348-AF81-58EFF7EEA8FA}"/>
+    <hyperlink ref="C130" r:id="rId15" tooltip="https://www.homedepot.com/p/339927440" display="https://www.homedepot.com/p/339927440" xr:uid="{34AFCD0E-8C12-A24A-828F-22505A90BE5F}"/>
+    <hyperlink ref="C131" r:id="rId16" tooltip="https://www.homedepot.com/p/339927441" display="https://www.homedepot.com/p/339927441" xr:uid="{91E7067B-523B-0543-BA7A-39DAE4E57F84}"/>
+    <hyperlink ref="C132" r:id="rId17" tooltip="https://www.homedepot.com/p/339927442" display="https://www.homedepot.com/p/339927442" xr:uid="{94ED3BB9-4382-B140-A9AA-8E2AFE42F2CF}"/>
+    <hyperlink ref="C133" r:id="rId18" tooltip="https://www.homedepot.com/p/339947312" display="https://www.homedepot.com/p/339947312" xr:uid="{D096ABEE-929C-8148-96F1-0DB77A7A4CA0}"/>
+    <hyperlink ref="C134" r:id="rId19" tooltip="https://www.homedepot.com/p/339927437" display="https://www.homedepot.com/p/339927437" xr:uid="{A7D2EEFA-BCE1-DA4A-93A0-BCC21EADC083}"/>
+    <hyperlink ref="C137" r:id="rId20" tooltip="http://www.homedepot.com/p/340312493" display="http://www.homedepot.com/p/340312493" xr:uid="{8BFD45A8-6B97-374E-A2E6-FA1EE0780DD6}"/>
+    <hyperlink ref="C138" r:id="rId21" tooltip="http://www.homedepot.com/p/340312481" display="http://www.homedepot.com/p/340312481" xr:uid="{7DA9E60B-FA8B-B549-8795-458ABD8B8A3D}"/>
+    <hyperlink ref="C139" r:id="rId22" tooltip="http://www.homedepot.com/p/340312476" display="http://www.homedepot.com/p/340312476" xr:uid="{F0B765B7-2EC2-9940-8CD8-248995C37761}"/>
+    <hyperlink ref="C140" r:id="rId23" tooltip="http://www.homedepot.com/p/340312489" display="http://www.homedepot.com/p/340312489" xr:uid="{B4E49CEA-5F25-0842-B5F2-A37995C490F1}"/>
+    <hyperlink ref="C141" r:id="rId24" tooltip="http://www.homedepot.com/p/340312486" display="http://www.homedepot.com/p/340312486" xr:uid="{F30F8C7B-779D-5A44-BD65-45F9B426C034}"/>
+    <hyperlink ref="C142" r:id="rId25" tooltip="http://www.homedepot.com/p/340312477" display="http://www.homedepot.com/p/340312477" xr:uid="{506B9C18-7659-C14A-ABCB-524662575D4D}"/>
+    <hyperlink ref="C143" r:id="rId26" tooltip="http://www.homedepot.com/p/340312479" display="http://www.homedepot.com/p/340312479" xr:uid="{75E6409F-9A58-B849-8E19-4E18B096902B}"/>
+    <hyperlink ref="C144" r:id="rId27" tooltip="http://www.homedepot.com/p/340312491" display="http://www.homedepot.com/p/340312491" xr:uid="{33BDB607-F61F-A74A-AFCE-5492A651B2B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LTL_qty.xlsx
+++ b/LTL_qty.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/BOL RDC/Data source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46C15978-587E-4460-BC84-0DB7B83CF2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B13ACB4-EF35-4153-8B1C-A684A1B206AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="150">
   <si>
     <t>D23_Floor and Wall Tiles</t>
   </si>
@@ -759,6 +759,9 @@
   </si>
   <si>
     <t>Urban White 12x24</t>
+  </si>
+  <si>
+    <t>URBAN WHITE &amp; ASH CHECKERBOARD 3X3 MOS</t>
   </si>
 </sst>
 </file>
@@ -3628,12 +3631,26 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B145" s="12"/>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>29</v>
+      </c>
+      <c r="B145" s="12">
+        <v>610110001491</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D145">
+        <v>7</v>
+      </c>
+      <c r="E145">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E127" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
-  <conditionalFormatting sqref="B2:B144">
+  <conditionalFormatting sqref="B2:B145">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <hyperlinks>
